--- a/testplan/testplan.xlsx
+++ b/testplan/testplan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HCMUS\THESIS\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HCMUS\UVM\testplan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B020B8F-4F58-49FC-BF9C-3C773DF4DA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796383D5-EB4F-4D09-BC18-DB14423A9E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{497B2DB0-8331-4D42-BF95-6562821218C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{497B2DB0-8331-4D42-BF95-6562821218C3}"/>
   </bookViews>
   <sheets>
     <sheet name="TESTCASES" sheetId="1" r:id="rId1"/>
@@ -542,24 +542,6 @@
     <t>Max Clock Frequency (Fmax​)</t>
   </si>
   <si>
-    <t>Verify basic execution flow of ALU and Pipeline.</t>
-  </si>
-  <si>
-    <t>Verify pipeline flush capability upon mispredicted branches.</t>
-  </si>
-  <si>
-    <t>Verify the transition into the trap handler.</t>
-  </si>
-  <si>
-    <t>Verify the sequential instruction fetch capability of the ICache.</t>
-  </si>
-  <si>
-    <t>Handle non-sequential fetch requests (due to Jump instructions).</t>
-  </si>
-  <si>
-    <t>Verify instruction/data coherency using FENCE.I.</t>
-  </si>
-  <si>
     <t>Verify MSHR allocation upon a Read Miss.</t>
   </si>
   <si>
@@ -590,24 +572,6 @@
     <t>Exhaust system resources (UVM Constrained Random).</t>
   </si>
   <si>
-    <t>Inject sequential Assembly instruction stream consisting of independent ADD, SUB, MUL, DIV operations.</t>
-  </si>
-  <si>
-    <t>Execute unpredictable conditional branch instructions (BNE, BEQ).</t>
-  </si>
-  <si>
-    <t>Trigger an External Interrupt or ECALL instruction while the instruction stream is running.</t>
-  </si>
-  <si>
-    <t>Core requests instructions at PC, PC+4, PC+8.</t>
-  </si>
-  <si>
-    <t>Jump to a distant PC (different Cacheline).</t>
-  </si>
-  <si>
-    <t>Execute FENCE.I instruction after self-modifying code.</t>
-  </si>
-  <si>
     <t>Core issues a LOAD instruction to address A (Miss).</t>
   </si>
   <si>
@@ -641,24 +605,6 @@
     <t>Continuously mix ALU, Jump, FENCE.I, and Load/Store instructions for 2 million cycles.</t>
   </si>
   <si>
-    <t>Pipeline does not stall incorrectly; GPR results match the Reference Model.</t>
-  </si>
-  <si>
-    <t>Pipeline flushes all invalid instructions, correctly updates to the new PC, and executes no garbage instructions.</t>
-  </si>
-  <si>
-    <t>PC jumps correctly to the mtvec address, saves the correct mepc, and resumes normal execution after MRET.</t>
-  </si>
-  <si>
-    <t>First access results in a Miss (triggers AXI read); subsequent accesses result in Hits, returning instructions in the correct cycle.</t>
-  </si>
-  <si>
-    <t>ICache cancels sequential prefetch (if any) and issues a new AXI request to the Jump address.</t>
-  </si>
-  <si>
-    <t>ICache flushes all valid bits, forcing a refetch of new code from Memory/L2.</t>
-  </si>
-  <si>
     <t>MSHR allocates the request and asserts AXI ARVALID. Data is returned to the Core correctly when AXI RVALID is asserted.</t>
   </si>
   <si>
@@ -696,6 +642,60 @@
   </si>
   <si>
     <t>Bins: USEFUL (Accessed by Core), WASTED (Evicted before use)</t>
+  </si>
+  <si>
+    <t>Verify decode, execute and write-back of integer ALU instructions using a bare-metal RISC-V program.</t>
+  </si>
+  <si>
+    <t>Verify branch/jump execution, PC redirection and pipeline flush.</t>
+  </si>
+  <si>
+    <t>Verify CSR access and synchronous exception handling (ECALL/illegal instruction).</t>
+  </si>
+  <si>
+    <t>Verify sequential instruction fetch, cache refill and cache hits.</t>
+  </si>
+  <si>
+    <t>Verify instruction fetch redirection after branch/jump.</t>
+  </si>
+  <si>
+    <t>Verify ICache invalidation after FENCE.I.</t>
+  </si>
+  <si>
+    <t>Load ALU program -&gt; Release reset -&gt; CPU executes ADD/SUB/AND/OR/XOR/SLT -&gt; Monitor commit and register write-back -&gt; Scoreboard compares GPR values.</t>
+  </si>
+  <si>
+    <t>Load branch program -&gt; Execute BEQ/BNE/JAL/JALR -&gt; Monitor PC trace and commit sequence -&gt; Compare expected control flow.</t>
+  </si>
+  <si>
+    <t>Load CSR/ECALL program -&gt; Execute CSR instructions and exception -&gt; Monitor CSR updates, mepc and mcause -&gt; Compare with expected results.</t>
+  </si>
+  <si>
+    <t>Execute linear instruction stream -&gt; Observe ICache requests and AXI refill -&gt; Continue execution after refill.</t>
+  </si>
+  <si>
+    <t>Execute branch-intensive program -&gt; Observe fetch cancellation and new fetch request after redirect.</t>
+  </si>
+  <si>
+    <t>Modify instruction memory -&gt; Execute FENCE.I -&gt; Re-fetch modified code -&gt; Monitor committed instructions.</t>
+  </si>
+  <si>
+    <t>All committed register values match reference model; no illegal commit; UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>Correct PC redirection, wrong-path instructions never commit, UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>CSR values, mepc and mcause are correct; execution resumes at correct handler; UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>First access causes refill; subsequent accesses hit in ICache; instructions execute correctly.</t>
+  </si>
+  <si>
+    <t>Old fetch is discarded, new fetch follows redirected PC, correct instruction sequence commits.</t>
+  </si>
+  <si>
+    <t>CPU executes updated instruction after FENCE.I; stale instructions are never executed; UVM_ERROR=0.</t>
   </si>
 </sst>
 </file>
@@ -1230,8 +1230,8 @@
     <col min="3" max="3" width="22.33203125" customWidth="1"/>
     <col min="4" max="4" width="29.6640625" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" customWidth="1"/>
-    <col min="7" max="7" width="47.6640625" customWidth="1"/>
+    <col min="6" max="6" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1275,13 +1275,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>47</v>
@@ -1299,13 +1299,13 @@
         <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>47</v>
@@ -1323,13 +1323,13 @@
         <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>48</v>
@@ -1349,13 +1349,13 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>47</v>
@@ -1373,13 +1373,13 @@
         <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>47</v>
@@ -1397,13 +1397,13 @@
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>49</v>
@@ -1423,13 +1423,13 @@
         <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>47</v>
@@ -1450,10 +1450,10 @@
         <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -1471,13 +1471,13 @@
         <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>48</v>
@@ -1497,13 +1497,13 @@
         <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
@@ -1521,13 +1521,13 @@
         <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>47</v>
@@ -1545,13 +1545,13 @@
         <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>48</v>
@@ -1569,13 +1569,13 @@
         <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
@@ -1595,13 +1595,13 @@
         <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>47</v>
@@ -1619,13 +1619,13 @@
         <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
@@ -1643,13 +1643,13 @@
         <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>47</v>
@@ -1667,13 +1667,13 @@
         <v>69</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -1896,7 +1896,7 @@
         <v>112</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,7 +1913,7 @@
         <v>113</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
